--- a/public/post/drafts/season-prediction/ladies_predictions.xlsx
+++ b/public/post/drafts/season-prediction/ladies_predictions.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -20,16 +20,10 @@
     <t xml:space="preserve">Nation</t>
   </si>
   <si>
-    <t xml:space="preserve">Pct_of_Max_Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predicted_Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI_Lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI_Upper</t>
+    <t xml:space="preserve">2023-24 Points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-25 Predicted Points</t>
   </si>
   <si>
     <t xml:space="preserve">Jessie Diggins</t>
@@ -41,12 +35,6 @@
     <t xml:space="preserve">0.760612940856018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.707932829727802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.813293051984233</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kerttu Niskanen</t>
   </si>
   <si>
@@ -56,24 +44,12 @@
     <t xml:space="preserve">0.706103927432444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.653174451216787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.759033403648101</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rosie Brennan</t>
   </si>
   <si>
     <t xml:space="preserve">0.671401367223218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616268685851637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.726534048594798</t>
-  </si>
-  <si>
     <t xml:space="preserve">Frida Karlsson</t>
   </si>
   <si>
@@ -83,36 +59,18 @@
     <t xml:space="preserve">0.670651590777622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623998578764763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.717304602790481</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linn Svahn</t>
   </si>
   <si>
     <t xml:space="preserve">0.664960989761124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607310708438774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.722611271083473</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jonna Sundling</t>
   </si>
   <si>
     <t xml:space="preserve">0.663914778162671</t>
   </si>
   <si>
-    <t xml:space="preserve">0.607386329924492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72044322640085</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tiril Udnes Weng</t>
   </si>
   <si>
@@ -122,12 +80,6 @@
     <t xml:space="preserve">0.544591114977866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484892338571236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.604289891384497</t>
-  </si>
-  <si>
     <t xml:space="preserve">Victoria Carl</t>
   </si>
   <si>
@@ -137,60 +89,30 @@
     <t xml:space="preserve">0.539624566361669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50075611456851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.578493018154828</t>
-  </si>
-  <si>
     <t xml:space="preserve">Heidi Weng</t>
   </si>
   <si>
     <t xml:space="preserve">0.529625625146681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48433534603192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.574915904261442</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ebba Andersson</t>
   </si>
   <si>
     <t xml:space="preserve">0.513205082517606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.46716103898578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.559249126049432</t>
-  </si>
-  <si>
     <t xml:space="preserve">Emma Ribom</t>
   </si>
   <si>
     <t xml:space="preserve">0.50974880110012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.465010323775294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.554487278424946</t>
-  </si>
-  <si>
     <t xml:space="preserve">Katharina Hennig</t>
   </si>
   <si>
     <t xml:space="preserve">0.505320191052195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462910641974718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.547729740129671</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nadine Fähndrich</t>
   </si>
   <si>
@@ -200,48 +122,24 @@
     <t xml:space="preserve">0.476721783171128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.430154070549383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.523289495792873</t>
-  </si>
-  <si>
     <t xml:space="preserve">Krista Pärmäkoski</t>
   </si>
   <si>
     <t xml:space="preserve">0.472771252424993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.432650756920224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.512891747929762</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anne Kjersti Kalvå</t>
   </si>
   <si>
     <t xml:space="preserve">0.457792740958984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417608497503312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.497976984414656</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maja Dahlqvist</t>
   </si>
   <si>
     <t xml:space="preserve">0.423503207613313</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377441775470515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.46956463975611</t>
-  </si>
-  <si>
     <t xml:space="preserve">Teresa Stadlober</t>
   </si>
   <si>
@@ -251,72 +149,36 @@
     <t xml:space="preserve">0.406398056684553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363044131805599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.449751981563508</t>
-  </si>
-  <si>
     <t xml:space="preserve">Johanna Matintalo</t>
   </si>
   <si>
     <t xml:space="preserve">0.402762809975917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36813631769862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.437389302253214</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lotta Udnes Weng</t>
   </si>
   <si>
     <t xml:space="preserve">0.400040641206878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356015618908246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44406566350551</t>
-  </si>
-  <si>
     <t xml:space="preserve">Astrid Øyre Slind</t>
   </si>
   <si>
     <t xml:space="preserve">0.399254727194729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.357626725448671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.440882728940786</t>
-  </si>
-  <si>
     <t xml:space="preserve">Laura Gimmler</t>
   </si>
   <si>
     <t xml:space="preserve">0.36927416487118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.325761026730922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412787303011437</t>
-  </si>
-  <si>
     <t xml:space="preserve">Moa Ilar</t>
   </si>
   <si>
     <t xml:space="preserve">0.357729087792739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.321803553207048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.39365462237843</t>
-  </si>
-  <si>
     <t xml:space="preserve">Katerina Janatova</t>
   </si>
   <si>
@@ -326,36 +188,18 @@
     <t xml:space="preserve">0.347173619565546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.310100862272299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.384246376858793</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jasmi Joensuu</t>
   </si>
   <si>
     <t xml:space="preserve">0.334549979294139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.300739505075081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.368360453513197</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pia Fink</t>
   </si>
   <si>
     <t xml:space="preserve">0.325121636434655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.288882722689879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.361360550179431</t>
-  </si>
-  <si>
     <t xml:space="preserve">Delphine Claudel</t>
   </si>
   <si>
@@ -365,36 +209,18 @@
     <t xml:space="preserve">0.312322954425418</t>
   </si>
   <si>
-    <t xml:space="preserve">0.27320018158376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.351445727267075</t>
-  </si>
-  <si>
     <t xml:space="preserve">Julia Kern</t>
   </si>
   <si>
     <t xml:space="preserve">0.307078828259042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.261838930005803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35231872651228</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kristine Stavås Skistad</t>
   </si>
   <si>
     <t xml:space="preserve">0.301763179855004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.255267652024723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.348258707685285</t>
-  </si>
-  <si>
     <t xml:space="preserve">Patricijia Eiduka</t>
   </si>
   <si>
@@ -404,132 +230,66 @@
     <t xml:space="preserve">0.301592198498324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265206872481803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.337977524514844</t>
-  </si>
-  <si>
     <t xml:space="preserve">Moa Lundgren</t>
   </si>
   <si>
     <t xml:space="preserve">0.299025014643917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268755526496842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.329294502790993</t>
-  </si>
-  <si>
     <t xml:space="preserve">Johanna Hagström</t>
   </si>
   <si>
     <t xml:space="preserve">0.289051393598556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245379635412281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.332723151784831</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mathilde Myhrvold</t>
   </si>
   <si>
     <t xml:space="preserve">0.282615092460134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.248021098725197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.31720908619507</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coletta Rydzek</t>
   </si>
   <si>
     <t xml:space="preserve">0.278152480063585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241794344058307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.314510616068864</t>
-  </si>
-  <si>
     <t xml:space="preserve">Margrethe Bergane</t>
   </si>
   <si>
     <t xml:space="preserve">0.247474077839094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214549408310223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.280398747367965</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sophia Laukli</t>
   </si>
   <si>
     <t xml:space="preserve">0.24608368574528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210582572593865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.281584798896695</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anne Kyllönen</t>
   </si>
   <si>
     <t xml:space="preserve">0.244354449878821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208640103564371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.28006879619327</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
   </si>
   <si>
     <t xml:space="preserve">0.232251896700113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.200084257045009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264419536355217</t>
-  </si>
-  <si>
     <t xml:space="preserve">Flora Dolci</t>
   </si>
   <si>
     <t xml:space="preserve">0.229239769849178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197817629088715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.260661910609641</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sofie Krehl</t>
   </si>
   <si>
     <t xml:space="preserve">0.229223069428369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193523339821069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.264922799035668</t>
-  </si>
-  <si>
     <t xml:space="preserve">Caterina Ganz</t>
   </si>
   <si>
@@ -539,84 +299,42 @@
     <t xml:space="preserve">0.205889566038756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171401231897778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.240377900179734</t>
-  </si>
-  <si>
     <t xml:space="preserve">Katherine Sauerbrey</t>
   </si>
   <si>
     <t xml:space="preserve">0.185847757945053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156411693752273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.215283822137832</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jasmin Kähärä</t>
   </si>
   <si>
     <t xml:space="preserve">0.172271850975565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140952001085513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.203591700865617</t>
-  </si>
-  <si>
     <t xml:space="preserve">Novie McCabe</t>
   </si>
   <si>
     <t xml:space="preserve">0.168298128808573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137878530341653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.198717727275493</t>
-  </si>
-  <si>
     <t xml:space="preserve">Desiree Steiner</t>
   </si>
   <si>
     <t xml:space="preserve">0.152881448229489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12575217664567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.180010719813308</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lena Quintin</t>
   </si>
   <si>
     <t xml:space="preserve">0.151399082027264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11707740471143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.185720759343097</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alina Meier</t>
   </si>
   <si>
     <t xml:space="preserve">0.148933792538332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.120530957726806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.177336627349857</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kathrine Stewart-Jones</t>
   </si>
   <si>
@@ -626,168 +344,84 @@
     <t xml:space="preserve">0.148806567641027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111406668317432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.186206466964623</t>
-  </si>
-  <si>
     <t xml:space="preserve">Katri Lylynperä</t>
   </si>
   <si>
     <t xml:space="preserve">0.146400380798565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11868275418848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174118007408649</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nicole Monsorno</t>
   </si>
   <si>
     <t xml:space="preserve">0.1402984684425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112983286724421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167613650160579</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tereza Beranova</t>
   </si>
   <si>
     <t xml:space="preserve">0.131563360224431</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0980512039999276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165075516448934</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anja Weber</t>
   </si>
   <si>
     <t xml:space="preserve">0.124652664773624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0972303145579363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152075014989312</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nadja Kälin</t>
   </si>
   <si>
     <t xml:space="preserve">0.12254572744397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0974037043411643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147687750546777</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sofia Henriksson</t>
   </si>
   <si>
     <t xml:space="preserve">0.108980251105994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0835532322938231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134407269918164</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lisa Lohmann</t>
   </si>
   <si>
     <t xml:space="preserve">0.108130197284681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.081174576071386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135085818497976</t>
-  </si>
-  <si>
     <t xml:space="preserve">Francesca Franchi</t>
   </si>
   <si>
     <t xml:space="preserve">0.106514165864273</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0778848654131571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135143466315389</t>
-  </si>
-  <si>
     <t xml:space="preserve">Melissa Gal</t>
   </si>
   <si>
     <t xml:space="preserve">0.105092602261243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0798937261856162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130291478336869</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lena Keck</t>
   </si>
   <si>
     <t xml:space="preserve">0.104516236815678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0812124300078853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12782004362347</t>
-  </si>
-  <si>
     <t xml:space="preserve">Juliette Ducordeau</t>
   </si>
   <si>
     <t xml:space="preserve">0.0936103468037112</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0635003640629319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123720329544491</t>
-  </si>
-  <si>
     <t xml:space="preserve">Samantha Smith</t>
   </si>
   <si>
     <t xml:space="preserve">0.091581081578173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0674927579237387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115669405232607</t>
-  </si>
-  <si>
     <t xml:space="preserve">Barbora Antosova</t>
   </si>
   <si>
     <t xml:space="preserve">0.0873467451906863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0644025735696529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11029091681172</t>
-  </si>
-  <si>
     <t xml:space="preserve">Izabela Marcisz</t>
   </si>
   <si>
@@ -797,24 +431,12 @@
     <t xml:space="preserve">0.0807867946865624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0536987183268687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107874871046256</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anna Comarella</t>
   </si>
   <si>
     <t xml:space="preserve">0.0785937931397927</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0445554120277898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112632174251796</t>
-  </si>
-  <si>
     <t xml:space="preserve">Keidy Kaasiku</t>
   </si>
   <si>
@@ -824,72 +446,36 @@
     <t xml:space="preserve">0.0774152505962687</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0511476842795565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103682816912981</t>
-  </si>
-  <si>
     <t xml:space="preserve">Liliane Gagnon</t>
   </si>
   <si>
     <t xml:space="preserve">0.077349783084493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0509606287512903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103738937417696</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sonjaa Schmidt</t>
   </si>
   <si>
     <t xml:space="preserve">0.0770075157191168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0543510429079274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0996639885303062</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vilma Ryytty</t>
   </si>
   <si>
     <t xml:space="preserve">0.0744227948374507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0518408838394222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0970047058354792</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kaidy Kaasiku</t>
   </si>
   <si>
     <t xml:space="preserve">0.0741145880328908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0513385808529498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0968905952128318</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tiia Olkkonen</t>
   </si>
   <si>
     <t xml:space="preserve">0.0736656335243075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.047642087370886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0996891796777289</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anja Mandeljc</t>
   </si>
   <si>
@@ -899,48 +485,24 @@
     <t xml:space="preserve">0.0730775658327796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0345592432651451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111595888400414</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lisa Ingesson</t>
   </si>
   <si>
     <t xml:space="preserve">0.0619472425875529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0378189404223501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0860755447527556</t>
-  </si>
-  <si>
     <t xml:space="preserve">Amelia Wells</t>
   </si>
   <si>
     <t xml:space="preserve">0.0602908186187825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.03588966698429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.084691970253275</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lea Fischer</t>
   </si>
   <si>
     <t xml:space="preserve">0.0576897246696482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0233277962667361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0920516530725604</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nadezhda Stepashkina</t>
   </si>
   <si>
@@ -950,79 +512,40 @@
     <t xml:space="preserve">0.0560036961664711</t>
   </si>
   <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122207627904829</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kseniya Shalygina</t>
   </si>
   <si>
     <t xml:space="preserve">0.055178233891102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116679238677491</t>
-  </si>
-  <si>
     <t xml:space="preserve">Anna Melnik</t>
   </si>
   <si>
     <t xml:space="preserve">0.0546784360025804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0228562833122957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0865005886928652</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kitija Auzina</t>
   </si>
   <si>
     <t xml:space="preserve">0.0541608830822548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0200991961736787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.088222569990831</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kamila Makhmutova</t>
   </si>
   <si>
     <t xml:space="preserve">0.0528811304257552</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0177975067706014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.087964754080909</t>
-  </si>
-  <si>
     <t xml:space="preserve">Darya Ryazhko</t>
   </si>
   <si>
     <t xml:space="preserve">0.0521498099766816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0147024133786548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0895972065747084</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alayna Sonnesyn</t>
   </si>
   <si>
     <t xml:space="preserve">0.0386378109257049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000332616403051926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0769430054483578</t>
   </si>
 </sst>
 </file>
@@ -1364,1591 +887,1111 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>0.800615384615385</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
         <v>0.602769230769231</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>0.623076923076923</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>0.694461538461538</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>0.781846153846154</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>0.640615384615385</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>0.190461538461538</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>0.658461538461538</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>0.521230769230769</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
         <v>0.444</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>0.542461538461538</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
         <v>0.482461538461538</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
         <v>0.288923076923077</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
         <v>0.331384615384615</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
         <v>0.235076923076923</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>0.315076923076923</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" t="s">
-        <v>74</v>
-      </c>
-      <c r="F17" t="s">
-        <v>75</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="C18" t="n">
         <v>0.361538461538462</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
         <v>0.285230769230769</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
         <v>0.324</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" t="s">
-        <v>87</v>
-      </c>
-      <c r="F20" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
         <v>0.272923076923077</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" t="s">
-        <v>91</v>
-      </c>
-      <c r="F21" t="s">
-        <v>92</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C22" t="n">
         <v>0.280923076923077</v>
       </c>
       <c r="D22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C23" t="n">
         <v>0.351076923076923</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23" t="s">
-        <v>99</v>
-      </c>
-      <c r="F23" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C24" t="n">
         <v>0.355076923076923</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>106</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
         <v>0.266769230769231</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" t="s">
-        <v>108</v>
-      </c>
-      <c r="F25" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C26" t="n">
         <v>0.237846153846154</v>
       </c>
       <c r="D26" t="s">
-        <v>111</v>
-      </c>
-      <c r="E26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" t="s">
-        <v>113</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C27" t="n">
         <v>0.300923076923077</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" t="s">
-        <v>117</v>
-      </c>
-      <c r="F27" t="s">
-        <v>118</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
         <v>0.290153846153846</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" t="s">
-        <v>121</v>
-      </c>
-      <c r="F28" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C29" t="n">
         <v>0.348</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
-      </c>
-      <c r="E29" t="s">
-        <v>125</v>
-      </c>
-      <c r="F29" t="s">
-        <v>126</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="C30" t="n">
         <v>0.303076923076923</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
-      </c>
-      <c r="E30" t="s">
-        <v>130</v>
-      </c>
-      <c r="F30" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C31" t="n">
         <v>0.270153846153846</v>
       </c>
       <c r="D31" t="s">
-        <v>133</v>
-      </c>
-      <c r="E31" t="s">
-        <v>134</v>
-      </c>
-      <c r="F31" t="s">
-        <v>135</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C32" t="n">
         <v>0.215692307692308</v>
       </c>
       <c r="D32" t="s">
-        <v>137</v>
-      </c>
-      <c r="E32" t="s">
-        <v>138</v>
-      </c>
-      <c r="F32" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C33" t="n">
         <v>0.287692307692308</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" t="s">
-        <v>142</v>
-      </c>
-      <c r="F33" t="s">
-        <v>143</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C34" t="n">
         <v>0.285846153846154</v>
       </c>
       <c r="D34" t="s">
-        <v>145</v>
-      </c>
-      <c r="E34" t="s">
-        <v>146</v>
-      </c>
-      <c r="F34" t="s">
-        <v>147</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C35" t="n">
         <v>0.295076923076923</v>
       </c>
       <c r="D35" t="s">
-        <v>149</v>
-      </c>
-      <c r="E35" t="s">
-        <v>150</v>
-      </c>
-      <c r="F35" t="s">
-        <v>151</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
         <v>0.290153846153846</v>
       </c>
       <c r="D36" t="s">
-        <v>153</v>
-      </c>
-      <c r="E36" t="s">
-        <v>154</v>
-      </c>
-      <c r="F36" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C37" t="n">
         <v>0.268923076923077</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
-      </c>
-      <c r="E37" t="s">
-        <v>158</v>
-      </c>
-      <c r="F37" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C38" t="n">
         <v>0.302153846153846</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
-      </c>
-      <c r="E38" t="s">
-        <v>162</v>
-      </c>
-      <c r="F38" t="s">
-        <v>163</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>164</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C39" t="n">
         <v>0.193230769230769</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
-      </c>
-      <c r="E39" t="s">
-        <v>166</v>
-      </c>
-      <c r="F39" t="s">
-        <v>167</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C40" t="n">
         <v>0.0836923076923077</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
-      </c>
-      <c r="E40" t="s">
-        <v>170</v>
-      </c>
-      <c r="F40" t="s">
-        <v>171</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="C41" t="n">
         <v>0.268</v>
       </c>
       <c r="D41" t="s">
-        <v>174</v>
-      </c>
-      <c r="E41" t="s">
-        <v>175</v>
-      </c>
-      <c r="F41" t="s">
-        <v>176</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>177</v>
+        <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C42" t="n">
         <v>0.174461538461538</v>
       </c>
       <c r="D42" t="s">
-        <v>178</v>
-      </c>
-      <c r="E42" t="s">
-        <v>179</v>
-      </c>
-      <c r="F42" t="s">
-        <v>180</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>181</v>
+        <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C43" t="n">
         <v>0.120615384615385</v>
       </c>
       <c r="D43" t="s">
-        <v>182</v>
-      </c>
-      <c r="E43" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>185</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C44" t="n">
         <v>0.0907692307692308</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
-      </c>
-      <c r="E44" t="s">
-        <v>187</v>
-      </c>
-      <c r="F44" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C45" t="n">
         <v>0.232923076923077</v>
       </c>
       <c r="D45" t="s">
-        <v>190</v>
-      </c>
-      <c r="E45" t="s">
-        <v>191</v>
-      </c>
-      <c r="F45" t="s">
-        <v>192</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>193</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C46" t="n">
         <v>0.167692307692308</v>
       </c>
       <c r="D46" t="s">
-        <v>194</v>
-      </c>
-      <c r="E46" t="s">
-        <v>195</v>
-      </c>
-      <c r="F46" t="s">
-        <v>196</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C47" t="n">
         <v>0.152615384615385</v>
       </c>
       <c r="D47" t="s">
-        <v>198</v>
-      </c>
-      <c r="E47" t="s">
-        <v>199</v>
-      </c>
-      <c r="F47" t="s">
-        <v>200</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>201</v>
+        <v>107</v>
       </c>
       <c r="B48" t="s">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="C48" t="n">
         <v>0.0812307692307692</v>
       </c>
       <c r="D48" t="s">
-        <v>203</v>
-      </c>
-      <c r="E48" t="s">
-        <v>204</v>
-      </c>
-      <c r="F48" t="s">
-        <v>205</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>206</v>
+        <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C49" t="n">
         <v>0.0907692307692308</v>
       </c>
       <c r="D49" t="s">
-        <v>207</v>
-      </c>
-      <c r="E49" t="s">
-        <v>208</v>
-      </c>
-      <c r="F49" t="s">
-        <v>209</v>
+        <v>111</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>210</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="C50" t="n">
         <v>0.108615384615385</v>
       </c>
       <c r="D50" t="s">
-        <v>211</v>
-      </c>
-      <c r="E50" t="s">
-        <v>212</v>
-      </c>
-      <c r="F50" t="s">
-        <v>213</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>214</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C51" t="n">
         <v>0.123384615384615</v>
       </c>
       <c r="D51" t="s">
-        <v>215</v>
-      </c>
-      <c r="E51" t="s">
-        <v>216</v>
-      </c>
-      <c r="F51" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>218</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C52" t="n">
         <v>0.110153846153846</v>
       </c>
       <c r="D52" t="s">
-        <v>219</v>
-      </c>
-      <c r="E52" t="s">
-        <v>220</v>
-      </c>
-      <c r="F52" t="s">
-        <v>221</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>222</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C53" t="n">
         <v>0.102769230769231</v>
       </c>
       <c r="D53" t="s">
-        <v>223</v>
-      </c>
-      <c r="E53" t="s">
-        <v>224</v>
-      </c>
-      <c r="F53" t="s">
-        <v>225</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C54" t="n">
         <v>0.137538461538462</v>
       </c>
       <c r="D54" t="s">
-        <v>227</v>
-      </c>
-      <c r="E54" t="s">
-        <v>228</v>
-      </c>
-      <c r="F54" t="s">
-        <v>229</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>230</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C55" t="n">
         <v>0.223384615384615</v>
       </c>
       <c r="D55" t="s">
-        <v>231</v>
-      </c>
-      <c r="E55" t="s">
-        <v>232</v>
-      </c>
-      <c r="F55" t="s">
-        <v>233</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>234</v>
+        <v>124</v>
       </c>
       <c r="B56" t="s">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="C56" t="n">
         <v>0.092</v>
       </c>
       <c r="D56" t="s">
-        <v>235</v>
-      </c>
-      <c r="E56" t="s">
-        <v>236</v>
-      </c>
-      <c r="F56" t="s">
-        <v>237</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>238</v>
+        <v>126</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C57" t="n">
         <v>0.127692307692308</v>
       </c>
       <c r="D57" t="s">
-        <v>239</v>
-      </c>
-      <c r="E57" t="s">
-        <v>240</v>
-      </c>
-      <c r="F57" t="s">
-        <v>241</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="B58" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C58" t="n">
         <v>0.072</v>
       </c>
       <c r="D58" t="s">
-        <v>243</v>
-      </c>
-      <c r="E58" t="s">
-        <v>244</v>
-      </c>
-      <c r="F58" t="s">
-        <v>245</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>246</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="C59" t="n">
         <v>0.0818461538461538</v>
       </c>
       <c r="D59" t="s">
-        <v>247</v>
-      </c>
-      <c r="E59" t="s">
-        <v>248</v>
-      </c>
-      <c r="F59" t="s">
-        <v>249</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>250</v>
+        <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C60" t="n">
         <v>0.101230769230769</v>
       </c>
       <c r="D60" t="s">
-        <v>251</v>
-      </c>
-      <c r="E60" t="s">
-        <v>252</v>
-      </c>
-      <c r="F60" t="s">
-        <v>253</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>254</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="C61" t="n">
         <v>0.0593846153846154</v>
       </c>
       <c r="D61" t="s">
-        <v>255</v>
-      </c>
-      <c r="E61" t="s">
-        <v>256</v>
-      </c>
-      <c r="F61" t="s">
-        <v>257</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>258</v>
+        <v>136</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>137</v>
       </c>
       <c r="C62" t="n">
         <v>0.0341538461538462</v>
       </c>
       <c r="D62" t="s">
-        <v>260</v>
-      </c>
-      <c r="E62" t="s">
-        <v>261</v>
-      </c>
-      <c r="F62" t="s">
-        <v>262</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>263</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
-        <v>173</v>
+        <v>93</v>
       </c>
       <c r="C63" t="n">
         <v>0.0858461538461538</v>
       </c>
       <c r="D63" t="s">
-        <v>264</v>
-      </c>
-      <c r="E63" t="s">
-        <v>265</v>
-      </c>
-      <c r="F63" t="s">
-        <v>266</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>267</v>
+        <v>141</v>
       </c>
       <c r="B64" t="s">
-        <v>268</v>
+        <v>142</v>
       </c>
       <c r="C64" t="n">
         <v>0.0427692307692308</v>
       </c>
       <c r="D64" t="s">
-        <v>269</v>
-      </c>
-      <c r="E64" t="s">
-        <v>270</v>
-      </c>
-      <c r="F64" t="s">
-        <v>271</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>272</v>
+        <v>144</v>
       </c>
       <c r="B65" t="s">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="C65" t="n">
         <v>0.072</v>
       </c>
       <c r="D65" t="s">
-        <v>273</v>
-      </c>
-      <c r="E65" t="s">
-        <v>274</v>
-      </c>
-      <c r="F65" t="s">
-        <v>275</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>276</v>
+        <v>146</v>
       </c>
       <c r="B66" t="s">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="C66" t="n">
         <v>0.0590769230769231</v>
       </c>
       <c r="D66" t="s">
-        <v>277</v>
-      </c>
-      <c r="E66" t="s">
-        <v>278</v>
-      </c>
-      <c r="F66" t="s">
-        <v>279</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>280</v>
+        <v>148</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C67" t="n">
         <v>0.068</v>
       </c>
       <c r="D67" t="s">
-        <v>281</v>
-      </c>
-      <c r="E67" t="s">
-        <v>282</v>
-      </c>
-      <c r="F67" t="s">
-        <v>283</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>284</v>
+        <v>150</v>
       </c>
       <c r="B68" t="s">
-        <v>268</v>
+        <v>142</v>
       </c>
       <c r="C68" t="n">
         <v>0.0526153846153846</v>
       </c>
       <c r="D68" t="s">
-        <v>285</v>
-      </c>
-      <c r="E68" t="s">
-        <v>286</v>
-      </c>
-      <c r="F68" t="s">
-        <v>287</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C69" t="n">
         <v>0.0781538461538462</v>
       </c>
       <c r="D69" t="s">
-        <v>289</v>
-      </c>
-      <c r="E69" t="s">
-        <v>290</v>
-      </c>
-      <c r="F69" t="s">
-        <v>291</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>292</v>
+        <v>154</v>
       </c>
       <c r="B70" t="s">
-        <v>293</v>
+        <v>155</v>
       </c>
       <c r="C70" t="n">
         <v>0.0547692307692308</v>
       </c>
       <c r="D70" t="s">
-        <v>294</v>
-      </c>
-      <c r="E70" t="s">
-        <v>295</v>
-      </c>
-      <c r="F70" t="s">
-        <v>296</v>
+        <v>156</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>297</v>
+        <v>157</v>
       </c>
       <c r="B71" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C71" t="n">
         <v>0.0541538461538462</v>
       </c>
       <c r="D71" t="s">
-        <v>298</v>
-      </c>
-      <c r="E71" t="s">
-        <v>299</v>
-      </c>
-      <c r="F71" t="s">
-        <v>300</v>
+        <v>158</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>301</v>
+        <v>159</v>
       </c>
       <c r="B72" t="s">
-        <v>202</v>
+        <v>108</v>
       </c>
       <c r="C72" t="n">
         <v>0.00892307692307692</v>
       </c>
       <c r="D72" t="s">
-        <v>302</v>
-      </c>
-      <c r="E72" t="s">
-        <v>303</v>
-      </c>
-      <c r="F72" t="s">
-        <v>304</v>
+        <v>160</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>305</v>
+        <v>161</v>
       </c>
       <c r="B73" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C73" t="n">
         <v>0.0636923076923077</v>
       </c>
       <c r="D73" t="s">
-        <v>306</v>
-      </c>
-      <c r="E73" t="s">
-        <v>307</v>
-      </c>
-      <c r="F73" t="s">
-        <v>308</v>
+        <v>162</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>309</v>
+        <v>163</v>
       </c>
       <c r="B74" t="s">
-        <v>310</v>
+        <v>164</v>
       </c>
       <c r="C74" t="n">
         <v>0.0883076923076923</v>
       </c>
       <c r="D74" t="s">
-        <v>311</v>
-      </c>
-      <c r="E74" t="s">
-        <v>312</v>
-      </c>
-      <c r="F74" t="s">
-        <v>313</v>
+        <v>165</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>314</v>
+        <v>166</v>
       </c>
       <c r="B75" t="s">
-        <v>310</v>
+        <v>164</v>
       </c>
       <c r="C75" t="n">
         <v>0.064</v>
       </c>
       <c r="D75" t="s">
-        <v>315</v>
-      </c>
-      <c r="E75" t="s">
-        <v>312</v>
-      </c>
-      <c r="F75" t="s">
-        <v>316</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>317</v>
+        <v>168</v>
       </c>
       <c r="B76" t="s">
-        <v>310</v>
+        <v>164</v>
       </c>
       <c r="C76" t="n">
         <v>0.0230769230769231</v>
       </c>
       <c r="D76" t="s">
-        <v>318</v>
-      </c>
-      <c r="E76" t="s">
-        <v>319</v>
-      </c>
-      <c r="F76" t="s">
-        <v>320</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>321</v>
+        <v>170</v>
       </c>
       <c r="B77" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="C77" t="n">
         <v>0.016</v>
       </c>
       <c r="D77" t="s">
-        <v>322</v>
-      </c>
-      <c r="E77" t="s">
-        <v>323</v>
-      </c>
-      <c r="F77" t="s">
-        <v>324</v>
+        <v>171</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>325</v>
+        <v>172</v>
       </c>
       <c r="B78" t="s">
-        <v>310</v>
+        <v>164</v>
       </c>
       <c r="C78" t="n">
         <v>0.0415384615384615</v>
       </c>
       <c r="D78" t="s">
-        <v>326</v>
-      </c>
-      <c r="E78" t="s">
-        <v>327</v>
-      </c>
-      <c r="F78" t="s">
-        <v>328</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>329</v>
+        <v>174</v>
       </c>
       <c r="B79" t="s">
-        <v>310</v>
+        <v>164</v>
       </c>
       <c r="C79" t="n">
         <v>0.00184615384615385</v>
       </c>
       <c r="D79" t="s">
-        <v>330</v>
-      </c>
-      <c r="E79" t="s">
-        <v>331</v>
-      </c>
-      <c r="F79" t="s">
-        <v>332</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>333</v>
+        <v>176</v>
       </c>
       <c r="B80" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C80" t="n">
         <v>0.0338461538461538</v>
       </c>
       <c r="D80" t="s">
-        <v>334</v>
-      </c>
-      <c r="E80" t="s">
-        <v>335</v>
-      </c>
-      <c r="F80" t="s">
-        <v>336</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
